--- a/Results/tables/05_descriptive_statistics.xlsx
+++ b/Results/tables/05_descriptive_statistics.xlsx
@@ -1,35 +1,176 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="returns_pct" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sentiment" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="returns_pct" sheetId="1" r:id="rId1"/>
+    <sheet name="sentiment" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
+  <si>
+    <t>series</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>mean_pct</t>
+  </si>
+  <si>
+    <t>std_pct</t>
+  </si>
+  <si>
+    <t>min_pct</t>
+  </si>
+  <si>
+    <t>p25</t>
+  </si>
+  <si>
+    <t>median</t>
+  </si>
+  <si>
+    <t>p75</t>
+  </si>
+  <si>
+    <t>max_pct</t>
+  </si>
+  <si>
+    <t>skewness</t>
+  </si>
+  <si>
+    <t>excess_kurtosis</t>
+  </si>
+  <si>
+    <t>r_Market</t>
+  </si>
+  <si>
+    <t>r_Automobile_Assembler</t>
+  </si>
+  <si>
+    <t>r_Automobile_Parts_Accessories</t>
+  </si>
+  <si>
+    <t>r_Cable_Electrical_Goods</t>
+  </si>
+  <si>
+    <t>r_Cement</t>
+  </si>
+  <si>
+    <t>r_Chemical</t>
+  </si>
+  <si>
+    <t>r_Commercial_Banks</t>
+  </si>
+  <si>
+    <t>r_Engineering</t>
+  </si>
+  <si>
+    <t>r_Fertilizer</t>
+  </si>
+  <si>
+    <t>r_Food_Personal_Care_Products</t>
+  </si>
+  <si>
+    <t>r_Glass_Ceramics</t>
+  </si>
+  <si>
+    <t>r_Insurance</t>
+  </si>
+  <si>
+    <t>r_Inv_Banks_Inv_Cos_Securities_Cos</t>
+  </si>
+  <si>
+    <t>r_Leather_Tanneries</t>
+  </si>
+  <si>
+    <t>r_Modarabas</t>
+  </si>
+  <si>
+    <t>r_Oil_Gas_Exploration_Companies</t>
+  </si>
+  <si>
+    <t>r_Oil_Gas_Marketing_Companies</t>
+  </si>
+  <si>
+    <t>r_Paper_Board_Packaging</t>
+  </si>
+  <si>
+    <t>r_Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>r_Power_Generation_Distribution</t>
+  </si>
+  <si>
+    <t>r_Refinery</t>
+  </si>
+  <si>
+    <t>r_Sugar_Allied_Industries</t>
+  </si>
+  <si>
+    <t>r_Technology_Communication</t>
+  </si>
+  <si>
+    <t>r_Textile_Composite</t>
+  </si>
+  <si>
+    <t>r_Textile_Spinning</t>
+  </si>
+  <si>
+    <t>r_Transport</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>std</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>S_All</t>
+  </si>
+  <si>
+    <t>S_Monetary</t>
+  </si>
+  <si>
+    <t>S_Fiscal</t>
+  </si>
+  <si>
+    <t>S_External</t>
+  </si>
+  <si>
+    <t>S_Energy</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,80 +189,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -409,1290 +483,1176 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>series</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>mean_pct</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>std_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>min_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>p25</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>median</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>p75</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>max_pct</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>skewness</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>excess_kurtosis</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>r_Market</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>1492</v>
+      </c>
+      <c r="C2">
         <v>0.1253</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>1.2753</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>-9.2171</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>-0.474</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>0.2056</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0.7941</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>8.9703</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>-0.413</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>7.4562</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>r_Automobile_Assembler</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C3" t="n">
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>1492</v>
+      </c>
+      <c r="C3">
         <v>0.1401</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>1.7186</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>-9.443899999999999</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>-0.7795</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>0.0914</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>1.0149</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>9.0253</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>0.0223</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>2.5537</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>r_Automobile_Parts_Accessories</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C4" t="n">
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>1492</v>
+      </c>
+      <c r="C4">
         <v>0.0764</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>1.7362</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>-9.8431</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>-0.8621</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>0.057</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>0.9792</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>9.4642</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>-0.0069</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>3.0867</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>r_Cable_Electrical_Goods</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
         <v>1491</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>0.0837</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>1.8801</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>-8.6503</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>-1.0357</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>0.0047</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>1.2058</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>9.244</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>0.0219</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>1.5534</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>r_Cement</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C6" t="n">
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>1492</v>
+      </c>
+      <c r="C6">
         <v>0.146</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>1.894</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>-9.4781</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>-0.8801</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>0.0675</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>1.0751</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>9.7927</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>0.2537</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>2.8554</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>r_Chemical</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C7" t="n">
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>1492</v>
+      </c>
+      <c r="C7">
         <v>0.1166</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>1.3418</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>-8.125999999999999</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>-0.5941</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>0.1699</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>0.8713</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>9.288399999999999</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>-0.1895</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>4.7616</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>r_Commercial_Banks</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C8" t="n">
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>1492</v>
+      </c>
+      <c r="C8">
         <v>0.1536</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>1.2886</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>-9.701499999999999</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>-0.5285</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>0.1219</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>0.7261</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>9.039199999999999</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>0.3684</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>7.9285</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>r_Engineering</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C9" t="n">
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>1492</v>
+      </c>
+      <c r="C9">
         <v>0.0791</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>1.9153</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>-11.4576</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>-0.9919</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>-0.0157</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>1.0358</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>10.4091</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>0.1212</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>3.2405</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>r_Fertilizer</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C10" t="n">
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>1492</v>
+      </c>
+      <c r="C10">
         <v>0.1761</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>1.4457</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>-9.912100000000001</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>-0.5735</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>0.1176</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>0.8971</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>9.9961</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>0.1963</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>6.7373</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>r_Food_Personal_Care_Products</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C11" t="n">
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <v>1492</v>
+      </c>
+      <c r="C11">
         <v>0.0945</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>1.3937</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>-8.357799999999999</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>-0.6048</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>0.1082</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>0.8538</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>9.238899999999999</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>-0.2965</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>4.8064</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>r_Glass_Ceramics</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C12" t="n">
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12">
+        <v>1492</v>
+      </c>
+      <c r="C12">
         <v>0.1011</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>1.8289</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>-10.1321</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>-0.883</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>0.0042</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>1.0598</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>10.0833</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>0.09</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>3.0255</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>r_Insurance</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C13" t="n">
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
+        <v>1492</v>
+      </c>
+      <c r="C13">
         <v>0.1303</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>1.3754</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>-7.3673</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>-0.6868</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>0.1652</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>0.954</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>7.543</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>-0.0969</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>2.5441</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>r_Inv_Banks_Inv_Cos_Securities_Cos</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C14" t="n">
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14">
+        <v>1492</v>
+      </c>
+      <c r="C14">
         <v>0.1339</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>1.6639</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>-11.3441</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>-0.7827</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>0.1543</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>1.0855</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>8.917999999999999</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>-0.2316</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>3.8086</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>r_Leather_Tanneries</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
         <v>1340</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>0.1547</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>1.9569</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>-9.361000000000001</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>-1.0929</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>0.127</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>1.3561</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>8.4046</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>0.0065</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>0.9025</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>r_Modarabas</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
         <v>1490</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>0.08799999999999999</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>2.5648</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>-11.6826</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>-1.4077</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>-0.0123</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>1.4535</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>11.2146</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>0.3183</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>1.7636</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>r_Oil_Gas_Exploration_Companies</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C17" t="n">
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17">
+        <v>1492</v>
+      </c>
+      <c r="C17">
         <v>0.127</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>1.5731</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>-8.4922</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>-0.7115</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>-0.0118</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>0.8849</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>9.7698</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>0.4331</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>3.8634</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>r_Oil_Gas_Marketing_Companies</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C18" t="n">
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18">
+        <v>1492</v>
+      </c>
+      <c r="C18">
         <v>0.1114</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>1.8296</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>-10.0854</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>-0.9132</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>0.0815</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>1.1176</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>9.730700000000001</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>-0.0564</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>3.4105</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>r_Paper_Board_Packaging</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C19" t="n">
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19">
+        <v>1492</v>
+      </c>
+      <c r="C19">
         <v>0.0688</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>1.5708</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>-9.8207</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>-0.7793</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>0.016</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>0.8955</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>9.420299999999999</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>0.004</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19">
         <v>4.9295</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>r_Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C20" t="n">
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20">
+        <v>1492</v>
+      </c>
+      <c r="C20">
         <v>0.0818</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>1.5744</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>-9.006500000000001</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>-0.732</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>-0.0012</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>0.837</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>9.0306</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20">
         <v>0.2997</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20">
         <v>5.1144</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>r_Power_Generation_Distribution</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C21" t="n">
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21">
+        <v>1492</v>
+      </c>
+      <c r="C21">
         <v>0.1676</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>1.4768</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>-9.6653</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>-0.6383</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>0.1626</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>0.9402</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>9.7332</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>0.1077</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21">
         <v>4.6292</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>r_Refinery</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C22" t="n">
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22">
+        <v>1492</v>
+      </c>
+      <c r="C22">
         <v>0.1365</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>2.728</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>-11.0213</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>-1.2794</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>-0.0755</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>1.4311</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>11.398</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>0.3081</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22">
         <v>1.6238</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>r_Sugar_Allied_Industries</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C23" t="n">
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23">
+        <v>1492</v>
+      </c>
+      <c r="C23">
         <v>0.1334</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>1.3283</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>-6.4993</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>-0.6058</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>0.092</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>0.8969</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>6.9815</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>0.0184</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23">
         <v>1.9345</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>r_Technology_Communication</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C24" t="n">
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24">
+        <v>1492</v>
+      </c>
+      <c r="C24">
         <v>0.1179</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>2.0968</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>-10.904</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>-0.9507</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>0.1038</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>1.2818</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>12.5432</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24">
         <v>0.0595</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24">
         <v>3.4032</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>r_Textile_Composite</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C25" t="n">
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25">
+        <v>1492</v>
+      </c>
+      <c r="C25">
         <v>0.1472</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>1.5013</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>-7.9704</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>-0.6876</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>0.1166</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>0.974</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>7.5989</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>-0.1407</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25">
         <v>2.3891</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>r_Textile_Spinning</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C26" t="n">
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26">
+        <v>1492</v>
+      </c>
+      <c r="C26">
         <v>0.1488</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>1.9566</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>-9.331200000000001</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>-0.9475</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>0.1178</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>1.2585</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>9.105499999999999</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>-0.0295</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26">
         <v>1.9934</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>r_Transport</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27">
         <v>1486</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>0.0847</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>1.8634</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>-8.3581</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>-0.9826</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>-0.0049</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>1.1229</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>9.6165</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27">
         <v>0.1063</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27">
         <v>1.8433</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>series</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>std</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>p25</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>median</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>p75</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>skewness</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>excess_kurtosis</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>S_All</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2">
+        <v>1492</v>
+      </c>
+      <c r="C2">
         <v>-0.1131</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.195</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>-0.5471</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>-0.244</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>-0.1254</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>-0.0057</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>0.8378</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>1.5591</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>6.0885</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>S_Monetary</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C3" t="n">
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3">
+        <v>1492</v>
+      </c>
+      <c r="C3">
         <v>-0.0712</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>0.315</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>-0.8303</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>-0.3233</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>-0.0707</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>0.1742</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>0.8283</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>0.0308</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>-0.7825</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>S_Fiscal</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C4" t="n">
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4">
+        <v>1492</v>
+      </c>
+      <c r="C4">
         <v>-0.1972</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>0.2269</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>-0.9530999999999999</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>-0.3519</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>-0.1944</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>-0.0606</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>0.5273</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>0.0694</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>0.1174</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>S_External</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C5" t="n">
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5">
+        <v>1492</v>
+      </c>
+      <c r="C5">
         <v>-0.0516</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>0.2159</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>-0.6781</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>-0.1896</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>-0.06320000000000001</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>0.06519999999999999</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>0.8378</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>0.9018</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>2.8909</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>S_Energy</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C6" t="n">
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6">
+        <v>1492</v>
+      </c>
+      <c r="C6">
         <v>-0.193</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>0.1514</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>-0.6308</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>-0.2971</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>-0.1935</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>-0.09619999999999999</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>0.3317</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>0.1545</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>-0.0412</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>